--- a/public/templates/examples/A-048-ExternalConnectionInventory-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-048-ExternalConnectionInventory-EXAMPLE-S.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Connections" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Relationships" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'External Connections'!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -261,6 +266,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,7 +863,7 @@
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="9" t="inlineStr"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ID</t>
@@ -893,7 +905,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>EXT-01</t>
@@ -929,10 +941,8 @@
           <t>County IT Contact</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="H12" s="28">
+        <v>46063</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
@@ -971,10 +981,8 @@
           <t>County IT Contact</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="H13" s="28">
+        <v>46063</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
@@ -1013,13 +1021,11 @@
           <t>County IT Contact</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
+      <c r="H14" s="28">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
           <t>EXT-04</t>
@@ -1055,10 +1061,8 @@
           <t>County IT Contact</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="H15" s="28">
+        <v>45787</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
@@ -1125,7 +1129,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-06-24)</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1142,6 @@
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1150,7 +1153,6 @@
       <c r="B25" s="25" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(F12:F21,"Y*")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1162,7 +1164,6 @@
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIF(F12:F21,"N*")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -1173,8 +1174,7 @@
       </c>
       <c r="B27" s="25" t="n"/>
       <c r="C27" s="13">
-        <f>COUNTIF(H12:H21,"&lt;"&amp;(TODAY()-365))</f>
-        <v/>
+        <f>COUNTIF(H12:H21,"&lt;"&amp;(DATE(2026,6,24)-365))</f>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1281,10 +1281,8 @@
           <t>/s/ Tracy Holloway</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="D40" s="27">
+        <v>46069</v>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
@@ -1303,10 +1301,8 @@
           <t>/s/ Marcus Reed</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="D41" s="27">
+        <v>46069</v>
       </c>
     </row>
     <row r="42"/>
@@ -1342,16 +1338,14 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="34.7" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="B45" s="26">
+        <v>46069</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
@@ -1368,11 +1362,11 @@
       <c r="G45" s="12" t="n"/>
     </row>
     <row r="46"/>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="2" t="n"/>
+    <row r="47">
+      <c r="A47"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:G6"/>
@@ -1400,18 +1394,11 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E12:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"Active,Under Review,Retired,Decommissioned"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1445,7 +1432,7 @@
       <c r="A2" s="9" t="inlineStr"/>
     </row>
     <row r="3"/>
-    <row r="4">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Trust ID</t>
@@ -1482,7 +1469,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34.7" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
           <t>TR-01</t>
@@ -1513,10 +1500,8 @@
           <t>County IT Contact</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="G5" s="28">
+        <v>46063</v>
       </c>
     </row>
     <row r="6">
@@ -1605,8 +1590,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>